--- a/Output/Monthly/2026-08/Database/CoPQ database 25.xlsx
+++ b/Output/Monthly/2026-08/Database/CoPQ database 25.xlsx
@@ -15970,7 +15970,7 @@
         </is>
       </c>
       <c r="B6" s="41" t="n">
-        <v>3333.75</v>
+        <v>3116.88</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>13.12</v>
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>533.4000000000001</v>
+        <v>498.7</v>
       </c>
     </row>
     <row r="35">
@@ -16662,13 +16662,11 @@
         </is>
       </c>
       <c r="B3" s="41" t="n">
-        <v>6737.58</v>
-      </c>
-      <c r="C3" s="41" t="n">
-        <v>1624.04</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C3" s="41" t="n"/>
       <c r="D3" s="41" t="n">
-        <v>1750.99</v>
+        <v>80</v>
       </c>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="43">
@@ -16707,15 +16705,9 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="B4" s="41" t="n">
-        <v>2179.06</v>
-      </c>
-      <c r="C4" s="41" t="n">
-        <v>447.06</v>
-      </c>
-      <c r="D4" s="41" t="n">
-        <v>237.83</v>
-      </c>
+      <c r="B4" s="41" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="41" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="43">
         <f>SUM(B4:E4)</f>
@@ -16740,9 +16732,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="41" t="n">
-        <v>101.9</v>
-      </c>
+      <c r="C5" s="41" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="43">
@@ -16775,9 +16765,7 @@
           <t>VH4</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
-        <v>3551.88</v>
-      </c>
+      <c r="B6" s="41" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
@@ -16810,15 +16798,9 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
-        <v>1298.72</v>
-      </c>
-      <c r="C7" s="37" t="n">
-        <v>665.74</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>4566.61</v>
-      </c>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
       <c r="E7" s="37" t="n"/>
       <c r="F7" s="37">
         <f>SUM(B7:E7)</f>
@@ -16850,12 +16832,8 @@
         </is>
       </c>
       <c r="B8" s="40" t="n"/>
-      <c r="C8" s="37" t="n">
-        <v>1595.58</v>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>522.27</v>
-      </c>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
       <c r="E8" s="37" t="n"/>
       <c r="F8" s="37">
         <f>SUM(B8:E8)</f>
@@ -16887,9 +16865,7 @@
         </is>
       </c>
       <c r="B9" s="40" t="n"/>
-      <c r="C9" s="37" t="n">
-        <v>493.08</v>
-      </c>
+      <c r="C9" s="37" t="n"/>
       <c r="D9" s="37" t="n"/>
       <c r="E9" s="37" t="n"/>
       <c r="F9" s="37">
@@ -17001,9 +16977,7 @@
           <t>JV2</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>31.5</v>
-      </c>
+      <c r="E16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17016,9 +16990,7 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>279</v>
-      </c>
+      <c r="E17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17031,9 +17003,7 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>11</v>
-      </c>
+      <c r="E18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17046,9 +17016,7 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>84.5</v>
-      </c>
+      <c r="E19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17098,17 +17066,13 @@
           <t>JVB</t>
         </is>
       </c>
-      <c r="B23" s="32" t="n">
-        <v>39553</v>
-      </c>
+      <c r="B23" s="32" t="n"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>JVB</t>
         </is>
       </c>
-      <c r="E23" s="32" t="n">
-        <v>55.5</v>
-      </c>
+      <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
     </row>
     <row r="24">
@@ -17117,17 +17081,13 @@
           <t>JV2</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n">
-        <v>44113</v>
-      </c>
+      <c r="B24" s="32" t="n"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>JV2</t>
         </is>
       </c>
-      <c r="E24" s="32" t="n">
-        <v>455</v>
-      </c>
+      <c r="E24" s="32" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17135,17 +17095,13 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B25" s="32" t="n">
-        <v>15701</v>
-      </c>
+      <c r="B25" s="32" t="n"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>JV</t>
         </is>
       </c>
-      <c r="E25" s="32" t="n">
-        <v>112.1</v>
-      </c>
+      <c r="E25" s="32" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17153,17 +17109,13 @@
           <t>VH3</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n">
-        <v>8108</v>
-      </c>
+      <c r="B26" s="32" t="n"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>VH3</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
-        <v>32.2</v>
-      </c>
+      <c r="E26" s="5" t="n"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>"</t>
@@ -17176,17 +17128,13 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="B27" s="32" t="n">
-        <v>11534</v>
-      </c>
+      <c r="B27" s="32" t="n"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>VH2</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>109.2</v>
-      </c>
+      <c r="E27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17194,17 +17142,13 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="B28" s="32" t="n">
-        <v>62242</v>
-      </c>
+      <c r="B28" s="32" t="n"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>VH</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>214.2000000000008</v>
-      </c>
+      <c r="E28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17267,16 +17211,11 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B33" s="32" t="n">
-        <v>14796</v>
-      </c>
+      <c r="B33" s="32" t="n"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>JV</t>
         </is>
-      </c>
-      <c r="E33" t="n">
-        <v>128</v>
       </c>
     </row>
     <row r="34">
@@ -17285,16 +17224,11 @@
           <t>VH4</t>
         </is>
       </c>
-      <c r="B34" s="32" t="n">
-        <v>36945</v>
-      </c>
+      <c r="B34" s="32" t="n"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>VH4</t>
         </is>
-      </c>
-      <c r="E34" t="n">
-        <v>568.3000000000002</v>
       </c>
     </row>
     <row r="35">
@@ -17303,16 +17237,11 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="B35" s="32" t="n">
-        <v>17932</v>
-      </c>
+      <c r="B35" s="32" t="n"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>VH2</t>
         </is>
-      </c>
-      <c r="E35" t="n">
-        <v>204.5</v>
       </c>
     </row>
     <row r="36">
@@ -17322,16 +17251,14 @@
         </is>
       </c>
       <c r="B36" s="32" t="n">
-        <v>120824</v>
+        <v>10</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>VH</t>
         </is>
       </c>
-      <c r="E36" s="36" t="n">
-        <v>455</v>
-      </c>
+      <c r="E36" s="36" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17466,13 +17393,11 @@
         </is>
       </c>
       <c r="B3" s="41" t="n">
-        <v>6737.58</v>
-      </c>
-      <c r="C3" s="41" t="n">
-        <v>1624.04</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C3" s="41" t="n"/>
       <c r="D3" s="41" t="n">
-        <v>1750.99</v>
+        <v>80</v>
       </c>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="43">
@@ -17511,15 +17436,9 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="B4" s="41" t="n">
-        <v>2179.06</v>
-      </c>
-      <c r="C4" s="41" t="n">
-        <v>447.06</v>
-      </c>
-      <c r="D4" s="41" t="n">
-        <v>237.83</v>
-      </c>
+      <c r="B4" s="41" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="41" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="43">
         <f>SUM(B4:E4)</f>
@@ -17544,9 +17463,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="41" t="n">
-        <v>101.9</v>
-      </c>
+      <c r="C5" s="41" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="43">
@@ -17579,9 +17496,7 @@
           <t>VH4</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
-        <v>3551.88</v>
-      </c>
+      <c r="B6" s="41" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
@@ -17614,15 +17529,9 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
-        <v>1298.72</v>
-      </c>
-      <c r="C7" s="37" t="n">
-        <v>665.74</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>4566.61</v>
-      </c>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
       <c r="E7" s="37" t="n"/>
       <c r="F7" s="37">
         <f>SUM(B7:E7)</f>
@@ -17654,12 +17563,8 @@
         </is>
       </c>
       <c r="B8" s="40" t="n"/>
-      <c r="C8" s="37" t="n">
-        <v>1595.58</v>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>522.27</v>
-      </c>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
       <c r="E8" s="37" t="n"/>
       <c r="F8" s="37">
         <f>SUM(B8:E8)</f>
@@ -17691,9 +17596,7 @@
         </is>
       </c>
       <c r="B9" s="40" t="n"/>
-      <c r="C9" s="37" t="n">
-        <v>493.08</v>
-      </c>
+      <c r="C9" s="37" t="n"/>
       <c r="D9" s="37" t="n"/>
       <c r="E9" s="37" t="n"/>
       <c r="F9" s="37">
@@ -17805,9 +17708,7 @@
           <t>JV2</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>31.5</v>
-      </c>
+      <c r="E16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17820,9 +17721,7 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>279</v>
-      </c>
+      <c r="E17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17835,9 +17734,7 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>11</v>
-      </c>
+      <c r="E18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17850,9 +17747,7 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>84.5</v>
-      </c>
+      <c r="E19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17902,17 +17797,13 @@
           <t>JVB</t>
         </is>
       </c>
-      <c r="B23" s="32" t="n">
-        <v>39553</v>
-      </c>
+      <c r="B23" s="32" t="n"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>JVB</t>
         </is>
       </c>
-      <c r="E23" s="32" t="n">
-        <v>55.5</v>
-      </c>
+      <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
     </row>
     <row r="24">
@@ -17921,17 +17812,13 @@
           <t>JV2</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n">
-        <v>44113</v>
-      </c>
+      <c r="B24" s="32" t="n"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>JV2</t>
         </is>
       </c>
-      <c r="E24" s="32" t="n">
-        <v>455</v>
-      </c>
+      <c r="E24" s="32" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17939,17 +17826,13 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B25" s="32" t="n">
-        <v>15701</v>
-      </c>
+      <c r="B25" s="32" t="n"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>JV</t>
         </is>
       </c>
-      <c r="E25" s="32" t="n">
-        <v>112.1</v>
-      </c>
+      <c r="E25" s="32" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17957,17 +17840,13 @@
           <t>VH3</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n">
-        <v>8108</v>
-      </c>
+      <c r="B26" s="32" t="n"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>VH3</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
-        <v>32.2</v>
-      </c>
+      <c r="E26" s="5" t="n"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>"</t>
@@ -17980,17 +17859,13 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="B27" s="32" t="n">
-        <v>11534</v>
-      </c>
+      <c r="B27" s="32" t="n"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>VH2</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>109.2</v>
-      </c>
+      <c r="E27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17998,17 +17873,13 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="B28" s="32" t="n">
-        <v>62242</v>
-      </c>
+      <c r="B28" s="32" t="n"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>VH</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>214.2000000000008</v>
-      </c>
+      <c r="E28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -18071,16 +17942,11 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B33" s="32" t="n">
-        <v>14796</v>
-      </c>
+      <c r="B33" s="32" t="n"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>JV</t>
         </is>
-      </c>
-      <c r="E33" t="n">
-        <v>128</v>
       </c>
     </row>
     <row r="34">
@@ -18089,16 +17955,11 @@
           <t>VH4</t>
         </is>
       </c>
-      <c r="B34" s="32" t="n">
-        <v>36945</v>
-      </c>
+      <c r="B34" s="32" t="n"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>VH4</t>
         </is>
-      </c>
-      <c r="E34" t="n">
-        <v>568.3000000000002</v>
       </c>
     </row>
     <row r="35">
@@ -18107,16 +17968,11 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="B35" s="32" t="n">
-        <v>17932</v>
-      </c>
+      <c r="B35" s="32" t="n"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>VH2</t>
         </is>
-      </c>
-      <c r="E35" t="n">
-        <v>204.5</v>
       </c>
     </row>
     <row r="36">
@@ -18126,16 +17982,14 @@
         </is>
       </c>
       <c r="B36" s="32" t="n">
-        <v>120824</v>
+        <v>10</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>VH</t>
         </is>
       </c>
-      <c r="E36" s="36" t="n">
-        <v>455</v>
-      </c>
+      <c r="E36" s="36" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">

--- a/Output/Monthly/2026-08/Database/CoPQ database 25.xlsx
+++ b/Output/Monthly/2026-08/Database/CoPQ database 25.xlsx
@@ -681,7 +681,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -770,6 +770,16 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15862,7 +15872,7 @@
         <v>1229.97</v>
       </c>
       <c r="D3" s="41" t="n">
-        <v>1574.5</v>
+        <v>1584.47</v>
       </c>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="43">
@@ -15908,7 +15918,7 @@
         <v>544.84</v>
       </c>
       <c r="D4" s="41" t="n">
-        <v>125.76</v>
+        <v>125.94</v>
       </c>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="43">
@@ -16013,7 +16023,7 @@
         <v>580.45</v>
       </c>
       <c r="D7" s="37" t="n">
-        <v>6554.62</v>
+        <v>6558.06</v>
       </c>
       <c r="E7" s="37" t="n"/>
       <c r="F7" s="37">
@@ -16047,10 +16057,10 @@
       </c>
       <c r="B8" s="40" t="n"/>
       <c r="C8" s="37" t="n">
-        <v>1837.15</v>
+        <v>1845.27</v>
       </c>
       <c r="D8" s="37" t="n">
-        <v>770.0700000000001</v>
+        <v>767.6900000000001</v>
       </c>
       <c r="E8" s="37" t="n"/>
       <c r="F8" s="37">
@@ -16322,7 +16332,7 @@
         </is>
       </c>
       <c r="E24" s="32" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="25">
@@ -16350,7 +16360,7 @@
         </is>
       </c>
       <c r="B26" s="32" t="n">
-        <v>12610</v>
+        <v>13872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -16661,13 +16671,9 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="B3" s="41" t="n">
-        <v>150</v>
-      </c>
+      <c r="B3" s="41" t="n"/>
       <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n">
-        <v>80</v>
-      </c>
+      <c r="D3" s="41" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="43">
         <f>SUM(B3:E3)</f>
@@ -17250,9 +17256,7 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="B36" s="32" t="n">
-        <v>10</v>
-      </c>
+      <c r="B36" s="32" t="n"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>VH</t>
@@ -17392,13 +17396,9 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="B3" s="41" t="n">
-        <v>150</v>
-      </c>
+      <c r="B3" s="41" t="n"/>
       <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n">
-        <v>80</v>
-      </c>
+      <c r="D3" s="41" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="43">
         <f>SUM(B3:E3)</f>
@@ -17981,9 +17981,7 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="B36" s="32" t="n">
-        <v>10</v>
-      </c>
+      <c r="B36" s="32" t="n"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>VH</t>

--- a/Output/Monthly/2026-08/Database/CoPQ database 25.xlsx
+++ b/Output/Monthly/2026-08/Database/CoPQ database 25.xlsx
@@ -15766,12 +15766,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N37"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.1833333333333" customWidth="1" style="20" min="1" max="1"/>
     <col width="15.6333333333333" customWidth="1" style="20" min="2" max="2"/>
     <col width="13.1833333333333" customWidth="1" style="20" min="3" max="3"/>
-    <col width="12.1833333333333" customWidth="1" style="20" min="4" max="6"/>
+    <col width="12.1833333333333" customWidth="1" style="20" min="4" max="4"/>
     <col width="21.725" customWidth="1" style="20" min="7" max="7"/>
     <col width="12.5416666666667" customWidth="1" style="20" min="10" max="10"/>
     <col width="11.5416666666667" customWidth="1" style="20" min="11" max="11"/>
@@ -15879,7 +15879,7 @@
         <f>SUM(B3:E3)</f>
         <v/>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="44">
         <f>B3+C3</f>
         <v/>
       </c>
@@ -15925,7 +15925,7 @@
         <f>SUM(B4:E4)</f>
         <v/>
       </c>
-      <c r="G4" s="38">
+      <c r="G4" s="44">
         <f>B4+C4</f>
         <v/>
       </c>
@@ -15953,7 +15953,7 @@
         <f>SUM(B5:E5)</f>
         <v/>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="44">
         <f>B5+C5</f>
         <v/>
       </c>
@@ -15991,7 +15991,7 @@
         <f>SUM(B6:E6)</f>
         <v/>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="44">
         <f>B6+C6</f>
         <v/>
       </c>
@@ -16016,21 +16016,21 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="39" t="n">
         <v>1308.72</v>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C7" s="39" t="n">
         <v>580.45</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="39" t="n">
         <v>6558.06</v>
       </c>
-      <c r="E7" s="37" t="n"/>
-      <c r="F7" s="37">
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39">
         <f>SUM(B7:E7)</f>
         <v/>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="44">
         <f>B7+C7</f>
         <v/>
       </c>
@@ -16055,19 +16055,19 @@
           <t>JV2</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n"/>
-      <c r="C8" s="37" t="n">
+      <c r="B8" s="45" t="n"/>
+      <c r="C8" s="39" t="n">
         <v>1845.27</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="39" t="n">
         <v>767.6900000000001</v>
       </c>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37">
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39">
         <f>SUM(B8:E8)</f>
         <v/>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="44">
         <f>B8+C8</f>
         <v/>
       </c>
@@ -16078,7 +16078,7 @@
           <t>CLG</t>
         </is>
       </c>
-      <c r="K8" s="37">
+      <c r="K8" s="39">
         <f>K6+K7</f>
         <v/>
       </c>
@@ -16092,24 +16092,24 @@
           <t>JVB</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n"/>
-      <c r="C9" s="37" t="n">
+      <c r="B9" s="45" t="n"/>
+      <c r="C9" s="39" t="n">
         <v>513.38</v>
       </c>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="37">
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39">
         <f>SUM(B9:E9)</f>
         <v/>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="44">
         <f>B9+C9</f>
         <v/>
       </c>
       <c r="H9" s="18" t="n"/>
       <c r="I9" s="18" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="17" t="n"/>
+      <c r="J9" s="46" t="n"/>
+      <c r="K9" s="46" t="n"/>
       <c r="L9" s="18" t="n"/>
       <c r="M9" s="18" t="n"/>
       <c r="N9" s="18" t="n"/>
@@ -16120,34 +16120,34 @@
           <t>CLG</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="39">
         <f>SUM(B3:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="39">
         <f>SUM(C3:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="39">
         <f>SUM(D3:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="39">
         <f>SUM(E3:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="39">
         <f>SUM(B10:E10)</f>
         <v/>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="44">
         <f>B10+C10</f>
         <v/>
       </c>
       <c r="H10" s="18" t="n"/>
       <c r="I10" s="18" t="n"/>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="17" t="n"/>
+      <c r="J10" s="46" t="n"/>
+      <c r="K10" s="46" t="n"/>
       <c r="L10" s="18" t="n"/>
       <c r="M10" s="18" t="n"/>
       <c r="N10" s="18" t="n"/>
@@ -16304,7 +16304,7 @@
           <t>JVB</t>
         </is>
       </c>
-      <c r="B23" s="32" t="n">
+      <c r="B23" s="33" t="n">
         <v>38959</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -16312,10 +16312,10 @@
           <t>JVB</t>
         </is>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="E23" s="33" t="n">
         <v>56.5</v>
       </c>
-      <c r="F23" s="32" t="n"/>
+      <c r="F23" s="33" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16323,7 +16323,7 @@
           <t>JV2</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n">
+      <c r="B24" s="33" t="n">
         <v>45571</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -16331,7 +16331,7 @@
           <t>JV2</t>
         </is>
       </c>
-      <c r="E24" s="32" t="n">
+      <c r="E24" s="33" t="n">
         <v>526</v>
       </c>
     </row>
@@ -16341,7 +16341,7 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B25" s="32" t="n">
+      <c r="B25" s="33" t="n">
         <v>13814</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -16349,7 +16349,7 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="E25" s="32" t="n">
+      <c r="E25" s="33" t="n">
         <v>95.8</v>
       </c>
     </row>
@@ -16359,7 +16359,7 @@
           <t>VH3</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n">
+      <c r="B26" s="33" t="n">
         <v>13872</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -16382,7 +16382,7 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="B27" s="32" t="n">
+      <c r="B27" s="33" t="n">
         <v>7801</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -16400,7 +16400,7 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="B28" s="32" t="n">
+      <c r="B28" s="33" t="n">
         <v>39210</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -16427,7 +16427,7 @@
           <t>CLG</t>
         </is>
       </c>
-      <c r="E29" s="36">
+      <c r="E29" s="47">
         <f>SUM(E23:E28)</f>
         <v/>
       </c>
@@ -16460,7 +16460,7 @@
           <t>JVB</t>
         </is>
       </c>
-      <c r="B32" s="32" t="n"/>
+      <c r="B32" s="33" t="n"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>JVB</t>
@@ -16473,7 +16473,7 @@
           <t>JV</t>
         </is>
       </c>
-      <c r="B33" s="32" t="n">
+      <c r="B33" s="33" t="n">
         <v>9740</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -16491,7 +16491,7 @@
           <t>VH4</t>
         </is>
       </c>
-      <c r="B34" s="32" t="n">
+      <c r="B34" s="33" t="n">
         <v>25794</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -16509,7 +16509,7 @@
           <t>VH2</t>
         </is>
       </c>
-      <c r="B35" s="32" t="n">
+      <c r="B35" s="33" t="n">
         <v>16934</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -16527,7 +16527,7 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="B36" s="32" t="n">
+      <c r="B36" s="33" t="n">
         <v>69184</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -16535,7 +16535,7 @@
           <t>VH</t>
         </is>
       </c>
-      <c r="E36" s="36" t="n">
+      <c r="E36" s="47" t="n">
         <v>368</v>
       </c>
     </row>
@@ -16560,8 +16560,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/Output/Monthly/2026-08/Database/CoPQ database 25.xlsx
+++ b/Output/Monthly/2026-08/Database/CoPQ database 25.xlsx
@@ -15980,11 +15980,9 @@
         </is>
       </c>
       <c r="B6" s="41" t="n">
-        <v>3116.88</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>13.12</v>
-      </c>
+        <v>3130</v>
+      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="43">
@@ -16409,7 +16407,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>123.2000000000001</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="29">
@@ -16492,7 +16490,7 @@
         </is>
       </c>
       <c r="B34" s="33" t="n">
-        <v>25794</v>
+        <v>25919</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -16500,7 +16498,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>498.7</v>
+        <v>500.8</v>
       </c>
     </row>
     <row r="35">
